--- a/실습파일/실습6_문항점검_올인원연계.xlsx
+++ b/실습파일/실습6_문항점검_올인원연계.xlsx
@@ -784,7 +784,7 @@
     <row r="29" ht="22" customHeight="1" s="17">
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [폴더 내 파일 목록 가져오기]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [폴더 내 파일 목록 가져오기]</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="36" ht="34" customHeight="1" s="17">
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [Gemini 실행] → [Gemini로 글과 파일(이미지, TXT, PDF, 음성 등) 행 단위 병렬 처리]</t>
+          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [Gemini 실행] → [Gemini로 글과 파일(이미지, TXT, PDF, 음성 등) 행 단위 병렬 처리]</t>
         </is>
       </c>
     </row>
@@ -919,14 +919,14 @@
     <row r="50" ht="34" customHeight="1" s="17">
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>24개를 다 읽을 필요가 없습니다. 프롬프트가 결과의  ## 오류 가능성  절 첫 줄에  오류 가능성 있음  또는  오류 가능성 없음  을 쓰도록 시켜 두었습니다.</t>
+          <t>12개를 다 읽을 필요가 없습니다. 프롬프트가 결과의  ## 오류 가능성  절 첫 줄에  오류 가능성 있음  또는  오류 가능성 없음  을 쓰도록 시켜 두었습니다.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" s="17">
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [하이라이트 처리]</t>
+          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [하이라이트 처리]</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
     <row r="55" ht="22" customHeight="1" s="17">
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4.  이어서 '범위 선택' 창이 뜨면 C2 부터 C25 까지 끌어 선택하고 [확인].</t>
+          <t>4.  이어서 '범위 선택' 창이 뜨면 C2 부터 C13 까지 끌어 선택하고 [확인].</t>
         </is>
       </c>
     </row>
